--- a/output/114→115分行表現分析_數據.xlsx
+++ b/output/114→115分行表現分析_數據.xlsx
@@ -9,11 +9,12 @@
   </bookViews>
   <sheets>
     <sheet name="分行明細" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="115達成分布" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="級距彙總" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="流向矩陣" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="缺口瀑布" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="未達75%情境" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="115達成說明" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="115達成分布" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="級距彙總" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="流向矩陣" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="缺口瀑布" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="未達75%情境" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="356">
   <si>
     <r>
       <rPr>
@@ -1472,7 +1473,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年年化達成率分布（簡報第</t>
+      <t xml:space="preserve">年財管手收達成說明（簡報第</t>
     </r>
     <r>
       <rPr>
@@ -1482,7 +1483,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">9</t>
     </r>
     <r>
       <rPr>
@@ -1491,68 +1492,14 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">頁）：依「分行明細」</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Q</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">欄（四捨五入</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">位，與原檔分群一致）以 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">COUNTIFS </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分組</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">達成率區間</t>
+      <t xml:space="preserve">頁）：全行與各通路區之目標、實績、達成率（公式引用「分行明細」）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">通路區</t>
+  </si>
+  <si>
+    <t xml:space="preserve">分行家數</t>
   </si>
   <si>
     <r>
@@ -1563,7 +1510,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">下限</t>
+      <t xml:space="preserve">超額</t>
     </r>
     <r>
       <rPr>
@@ -1574,7 +1521,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">/</t>
     </r>
     <r>
       <rPr>
@@ -1584,8 +1531,16 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">含</t>
-    </r>
+      <t xml:space="preserve">缺口</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">達標家數</t>
+  </si>
+  <si>
+    <t xml:space="preserve">達標比例</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -1595,10 +1550,8 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">115</t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -1607,7 +1560,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">上限</t>
+      <t xml:space="preserve">目標較</t>
     </r>
     <r>
       <rPr>
@@ -1618,7 +1571,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">114</t>
     </r>
     <r>
       <rPr>
@@ -1628,8 +1581,10 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">不含</t>
-    </r>
+      <t xml:space="preserve">目標成長</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -1639,359 +1594,222 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">分行家數</t>
-  </si>
-  <si>
-    <t xml:space="preserve">占比</t>
-  </si>
-  <si>
-    <t xml:space="preserve">累計家數</t>
-  </si>
-  <si>
-    <t xml:space="preserve">累計占比</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未達</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">60%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">70%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">70</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">75%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">75</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">80%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">80</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">90%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">90</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">110%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">110</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">120%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">120</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">130%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">130</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">150%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">150</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">180%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">180%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以上</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">統計值</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">達標分行數（≥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100%</t>
+      <t xml:space="preserve">115</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">實績較</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">114</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">實績成長</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">全行合計</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">115</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-9</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月進度（原檔「</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">115_</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分行業績」第</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列合計，輸入值）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月實績</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月目標進度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月達成率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隱含年化係數（分行明細年化實績合計</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷1-9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月實績）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原檔註記年化係數（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11.5/9</t>
     </r>
     <r>
       <rPr>
@@ -2000,417 +1818,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未達標分行數（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt;100%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未達</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">75%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分行數</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">達成率中位數</t>
-  </si>
-  <si>
-    <t xml:space="preserve">達成率簡單平均</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">達成率加權平均（全行實績</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">÷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">目標）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">最低達成率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最高達成率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115TYPE</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">115</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年達成率級距</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">達成率</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">超額</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">缺口</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">150%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以上，未達</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">180%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">120%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以上，未達</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">150%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以上，未達</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">120%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">75%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以上，未達</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未達</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">75%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">依</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">114</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年達成率級距（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">114TYPE</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）彙總 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">115 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年目標與實績（簡報第</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">頁數據）</t>
     </r>
   </si>
   <si>
@@ -2421,7 +1828,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">全部為公式（</t>
+      <t xml:space="preserve">註：原檔「</t>
     </r>
     <r>
       <rPr>
@@ -2431,7 +1838,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">COUNTIFS</t>
+      <t xml:space="preserve">116</t>
     </r>
     <r>
       <rPr>
@@ -2440,7 +1847,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">／</t>
+      <t xml:space="preserve">目標底稿</t>
     </r>
     <r>
       <rPr>
@@ -2450,7 +1857,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">SUMIFS </t>
+      <t xml:space="preserve">ver1</t>
     </r>
     <r>
       <rPr>
@@ -2459,6 +1866,1073 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">欄註記年化方式為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/9×11.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.278</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），但分行明細年化實績合計</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷1-9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月實績之隱含係數為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.269</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，兩者略有差異，建議確認原檔年化口徑。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">115</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年年化達成率分布（簡報第</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁）：依「分行明細」</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">欄（四捨五入</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位，與原檔分群一致）以 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">COUNTIFS </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分組</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">達成率區間</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下限</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">含</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上限</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不含</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">占比</t>
+  </si>
+  <si>
+    <t xml:space="preserve">累計家數</t>
+  </si>
+  <si>
+    <t xml:space="preserve">累計占比</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未達</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">110%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">110</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">120%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">120</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">130%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">130</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">150%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">150</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">180%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">180%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以上</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">統計值</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">達標分行數（≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未達標分行數（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt;100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未達</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分行數</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">達成率中位數</t>
+  </si>
+  <si>
+    <t xml:space="preserve">達成率簡單平均</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">達成率加權平均（全行實績</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">最低達成率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最高達成率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115TYPE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">115</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年達成率級距</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">達成率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">150%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以上，未達</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">180%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">120%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以上，未達</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">150%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以上，未達</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">120%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以上，未達</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未達</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">依</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">114</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年達成率級距（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">114TYPE</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）彙總 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">115 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年目標與實績（簡報第</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁數據）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全部為公式（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">COUNTIFS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SUMIFS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">引用「分行明細」）。</t>
     </r>
   </si>
@@ -3275,9 +3749,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">全行合計</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -3324,7 +3795,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
     <r>
       <rPr>
@@ -3982,7 +4453,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
     <r>
       <rPr>
@@ -4523,7 +4994,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
     <r>
       <rPr>
@@ -4923,15 +5394,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.00"/>
-    <numFmt numFmtId="168" formatCode="0"/>
-    <numFmt numFmtId="169" formatCode="General"/>
-    <numFmt numFmtId="170" formatCode="0.00;\(0.00\);\-"/>
-    <numFmt numFmtId="171" formatCode="\+0.0%;\-0.0%"/>
+    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.00"/>
+    <numFmt numFmtId="170" formatCode="0"/>
+    <numFmt numFmtId="171" formatCode="General"/>
+    <numFmt numFmtId="172" formatCode="0.00;\(0.00\);\-"/>
+    <numFmt numFmtId="173" formatCode="\+0.0%;\-0.0%"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -5137,7 +5610,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5198,7 +5671,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5206,19 +5679,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5230,19 +5711,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="169" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5258,7 +5743,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5266,15 +5751,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -16658,13 +17139,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16672,693 +17158,416 @@
         <v>217</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="I3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="M3" s="4" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="B4" s="15" t="n">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="B4" s="14" t="n">
+        <f aca="false">COUNTIFS(分行明細!$B$5:$B$187,A4)</f>
+        <v>46</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D4" s="14" t="n">
-        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B4,分行明細!$Q$5:$Q$187,"&lt;"&amp;C4)</f>
-        <v>2</v>
+        <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$B$5:$B$187,A4)</f>
+        <v>2963010000</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$B$5:$B$187,A4)</f>
+        <v>3171074682</v>
       </c>
       <c r="E4" s="16" t="n">
-        <f aca="false">D4/$D$16</f>
-        <v>0.0109289617486339</v>
-      </c>
-      <c r="F4" s="14" t="n">
-        <f aca="false">SUM($D$4:D4)</f>
-        <v>2</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <f aca="false">F4/$D$16</f>
-        <v>0.0109289617486339</v>
+        <f aca="false">IFERROR(D4/C4,0)</f>
+        <v>1.07022071542114</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <f aca="false">D4-C4</f>
+        <v>208064682</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <f aca="false">COUNTIFS(分行明細!$B$5:$B$187,A4,分行明細!$N$5:$N$187,"&gt;=0")</f>
+        <v>23</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <f aca="false">IFERROR(G4/B4,0)</f>
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$G$5:$G$187,分行明細!$B$5:$B$187,A4)</f>
+        <v>2525070000</v>
+      </c>
+      <c r="J4" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$H$5:$H$187,分行明細!$B$5:$B$187,A4)</f>
+        <v>2244221087</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <f aca="false">IFERROR(J4/I4,0)</f>
+        <v>0.888775791166186</v>
+      </c>
+      <c r="L4" s="16" t="n">
+        <f aca="false">IFERROR(C4/I4-1,0)</f>
+        <v>0.17343677601017</v>
+      </c>
+      <c r="M4" s="16" t="n">
+        <f aca="false">IFERROR(D4/J4-1,0)</f>
+        <v>0.412995671580195</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="B5" s="15" t="n">
-        <v>0.6</v>
+      <c r="A5" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="14" t="n">
+        <f aca="false">COUNTIFS(分行明細!$B$5:$B$187,A5)</f>
+        <v>36</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D5" s="17" t="n">
-        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B5,分行明細!$Q$5:$Q$187,"&lt;"&amp;C5)</f>
-        <v>7</v>
+        <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$B$5:$B$187,A5)</f>
+        <v>2425440000</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$B$5:$B$187,A5)</f>
+        <v>2761623404</v>
       </c>
       <c r="E5" s="16" t="n">
-        <f aca="false">D5/$D$16</f>
-        <v>0.0382513661202186</v>
-      </c>
-      <c r="F5" s="17" t="n">
-        <f aca="false">SUM($D$4:D5)</f>
-        <v>9</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <f aca="false">F5/$D$16</f>
-        <v>0.0491803278688525</v>
+        <f aca="false">IFERROR(D5/C5,0)</f>
+        <v>1.13860718220199</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <f aca="false">D5-C5</f>
+        <v>336183404</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <f aca="false">COUNTIFS(分行明細!$B$5:$B$187,A5,分行明細!$N$5:$N$187,"&gt;=0")</f>
+        <v>23</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <f aca="false">IFERROR(G5/B5,0)</f>
+        <v>0.638888888888889</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$G$5:$G$187,分行明細!$B$5:$B$187,A5)</f>
+        <v>2042820000</v>
+      </c>
+      <c r="J5" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$H$5:$H$187,分行明細!$B$5:$B$187,A5)</f>
+        <v>1992717357</v>
+      </c>
+      <c r="K5" s="16" t="n">
+        <f aca="false">IFERROR(J5/I5,0)</f>
+        <v>0.975473784768115</v>
+      </c>
+      <c r="L5" s="16" t="n">
+        <f aca="false">IFERROR(C5/I5-1,0)</f>
+        <v>0.187299908949393</v>
+      </c>
+      <c r="M5" s="16" t="n">
+        <f aca="false">IFERROR(D5/J5-1,0)</f>
+        <v>0.385858056737948</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="B6" s="15" t="n">
-        <v>0.7</v>
+      <c r="A6" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="14" t="n">
+        <f aca="false">COUNTIFS(分行明細!$B$5:$B$187,A6)</f>
+        <v>33</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D6" s="17" t="n">
-        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B6,分行明細!$Q$5:$Q$187,"&lt;"&amp;C6)</f>
-        <v>10</v>
+        <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$B$5:$B$187,A6)</f>
+        <v>1918680000</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$B$5:$B$187,A6)</f>
+        <v>1972630435</v>
       </c>
       <c r="E6" s="16" t="n">
-        <f aca="false">D6/$D$16</f>
-        <v>0.0546448087431694</v>
-      </c>
-      <c r="F6" s="17" t="n">
-        <f aca="false">SUM($D$4:D6)</f>
-        <v>19</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <f aca="false">F6/$D$16</f>
-        <v>0.103825136612022</v>
+        <f aca="false">IFERROR(D6/C6,0)</f>
+        <v>1.02811851637584</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <f aca="false">D6-C6</f>
+        <v>53950435</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <f aca="false">COUNTIFS(分行明細!$B$5:$B$187,A6,分行明細!$N$5:$N$187,"&gt;=0")</f>
+        <v>18</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <f aca="false">IFERROR(G6/B6,0)</f>
+        <v>0.545454545454545</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$G$5:$G$187,分行明細!$B$5:$B$187,A6)</f>
+        <v>1592200000</v>
+      </c>
+      <c r="J6" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$H$5:$H$187,分行明細!$B$5:$B$187,A6)</f>
+        <v>1535016328</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <f aca="false">IFERROR(J6/I6,0)</f>
+        <v>0.964085119959804</v>
+      </c>
+      <c r="L6" s="16" t="n">
+        <f aca="false">IFERROR(C6/I6-1,0)</f>
+        <v>0.205049616882301</v>
+      </c>
+      <c r="M6" s="16" t="n">
+        <f aca="false">IFERROR(D6/J6-1,0)</f>
+        <v>0.28508759093799</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
-        <v>228</v>
-      </c>
-      <c r="B7" s="15" t="n">
-        <v>0.75</v>
+      <c r="A7" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="14" t="n">
+        <f aca="false">COUNTIFS(分行明細!$B$5:$B$187,A7)</f>
+        <v>31</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D7" s="17" t="n">
-        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B7,分行明細!$Q$5:$Q$187,"&lt;"&amp;C7)</f>
-        <v>12</v>
+        <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$B$5:$B$187,A7)</f>
+        <v>2196530000</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$B$5:$B$187,A7)</f>
+        <v>2256636774</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">D7/$D$16</f>
-        <v>0.0655737704918033</v>
-      </c>
-      <c r="F7" s="17" t="n">
-        <f aca="false">SUM($D$4:D7)</f>
-        <v>31</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <f aca="false">F7/$D$16</f>
-        <v>0.169398907103825</v>
+        <f aca="false">IFERROR(D7/C7,0)</f>
+        <v>1.02736442206571</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <f aca="false">D7-C7</f>
+        <v>60106774</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <f aca="false">COUNTIFS(分行明細!$B$5:$B$187,A7,分行明細!$N$5:$N$187,"&gt;=0")</f>
+        <v>15</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <f aca="false">IFERROR(G7/B7,0)</f>
+        <v>0.483870967741936</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$G$5:$G$187,分行明細!$B$5:$B$187,A7)</f>
+        <v>1858140000</v>
+      </c>
+      <c r="J7" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$H$5:$H$187,分行明細!$B$5:$B$187,A7)</f>
+        <v>1955963390</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <f aca="false">IFERROR(J7/I7,0)</f>
+        <v>1.0526458662964</v>
+      </c>
+      <c r="L7" s="16" t="n">
+        <f aca="false">IFERROR(C7/I7-1,0)</f>
+        <v>0.182112219746628</v>
+      </c>
+      <c r="M7" s="16" t="n">
+        <f aca="false">IFERROR(D7/J7-1,0)</f>
+        <v>0.15372137614498</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="B8" s="15" t="n">
-        <v>0.8</v>
+      <c r="A8" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="B8" s="14" t="n">
+        <f aca="false">COUNTIFS(分行明細!$B$5:$B$187,A8)</f>
+        <v>37</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D8" s="17" t="n">
-        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B8,分行明細!$Q$5:$Q$187,"&lt;"&amp;C8)</f>
-        <v>24</v>
+        <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$B$5:$B$187,A8)</f>
+        <v>2281720000</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$B$5:$B$187,A8)</f>
+        <v>2323634074</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">D8/$D$16</f>
-        <v>0.131147540983607</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <f aca="false">SUM($D$4:D8)</f>
-        <v>55</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <f aca="false">F8/$D$16</f>
-        <v>0.300546448087432</v>
+        <f aca="false">IFERROR(D8/C8,0)</f>
+        <v>1.01836950809039</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <f aca="false">D8-C8</f>
+        <v>41914074</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <f aca="false">COUNTIFS(分行明細!$B$5:$B$187,A8,分行明細!$N$5:$N$187,"&gt;=0")</f>
+        <v>20</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <f aca="false">IFERROR(G8/B8,0)</f>
+        <v>0.540540540540541</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$G$5:$G$187,分行明細!$B$5:$B$187,A8)</f>
+        <v>1857310000</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$H$5:$H$187,分行明細!$B$5:$B$187,A8)</f>
+        <v>1901673999</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <f aca="false">IFERROR(J8/I8,0)</f>
+        <v>1.02388615739968</v>
+      </c>
+      <c r="L8" s="16" t="n">
+        <f aca="false">IFERROR(C8/I8-1,0)</f>
+        <v>0.228507895827837</v>
+      </c>
+      <c r="M8" s="16" t="n">
+        <f aca="false">IFERROR(D8/J8-1,0)</f>
+        <v>0.221888754445761</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="B9" s="17" t="n">
+        <f aca="false">SUM(B4:B8)</f>
+        <v>183</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <f aca="false">SUM(C4:C8)</f>
+        <v>11785380000</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <f aca="false">SUM(D4:D8)</f>
+        <v>12485599369</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <f aca="false">D9/C9</f>
+        <v>1.05941423772505</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <f aca="false">SUM(F4:F8)</f>
+        <v>700219369</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <f aca="false">SUM(G4:G8)</f>
+        <v>99</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <f aca="false">G9/B9</f>
+        <v>0.540983606557377</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <f aca="false">SUM(I4:I8)</f>
+        <v>9875540000</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <f aca="false">SUM(J4:J8)</f>
+        <v>9629592161</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <f aca="false">J9/I9</f>
+        <v>0.975095251601431</v>
+      </c>
+      <c r="L9" s="19" t="n">
+        <f aca="false">C9/I9-1</f>
+        <v>0.193390943685105</v>
+      </c>
+      <c r="M9" s="19" t="n">
+        <f aca="false">D9/J9-1</f>
+        <v>0.296586517917848</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="B12" s="22" t="n">
+        <v>9842349930.85</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="B13" s="22" t="n">
+        <v>9291037000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="B14" s="16" t="n">
+        <f aca="false">B12/B13</f>
+        <v>1.05933814824438</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="B9" s="15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C9" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="17" t="n">
-        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B9,分行明細!$Q$5:$Q$187,"&lt;"&amp;C9)</f>
-        <v>29</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <f aca="false">D9/$D$16</f>
-        <v>0.158469945355191</v>
-      </c>
-      <c r="F9" s="17" t="n">
-        <f aca="false">SUM($D$4:D9)</f>
-        <v>84</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <f aca="false">F9/$D$16</f>
-        <v>0.459016393442623</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
+      <c r="B15" s="24" t="n">
+        <f aca="false">分行明細!K188/B12</f>
+        <v>1.26855877475611</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="B10" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D10" s="17" t="n">
-        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B10,分行明細!$Q$5:$Q$187,"&lt;"&amp;C10)</f>
-        <v>25</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <f aca="false">D10/$D$16</f>
-        <v>0.136612021857924</v>
-      </c>
-      <c r="F10" s="17" t="n">
-        <f aca="false">SUM($D$4:D10)</f>
-        <v>109</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <f aca="false">F10/$D$16</f>
-        <v>0.595628415300546</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
+      <c r="B16" s="24" t="n">
+        <f aca="false">11.5/9</f>
+        <v>1.27777777777778</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="B11" s="15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C11" s="15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D11" s="17" t="n">
-        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B11,分行明細!$Q$5:$Q$187,"&lt;"&amp;C11)</f>
-        <v>27</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <f aca="false">D11/$D$16</f>
-        <v>0.147540983606557</v>
-      </c>
-      <c r="F11" s="17" t="n">
-        <f aca="false">SUM($D$4:D11)</f>
-        <v>136</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <f aca="false">F11/$D$16</f>
-        <v>0.743169398907104</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="B12" s="15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C12" s="15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B12,分行明細!$Q$5:$Q$187,"&lt;"&amp;C12)</f>
-        <v>17</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <f aca="false">D12/$D$16</f>
-        <v>0.092896174863388</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <f aca="false">SUM($D$4:D12)</f>
-        <v>153</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <f aca="false">F12/$D$16</f>
-        <v>0.836065573770492</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
-        <v>234</v>
-      </c>
-      <c r="B13" s="15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D13" s="17" t="n">
-        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B13,分行明細!$Q$5:$Q$187,"&lt;"&amp;C13)</f>
-        <v>23</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <f aca="false">D13/$D$16</f>
-        <v>0.12568306010929</v>
-      </c>
-      <c r="F13" s="17" t="n">
-        <f aca="false">SUM($D$4:D13)</f>
-        <v>176</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <f aca="false">F13/$D$16</f>
-        <v>0.961748633879781</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="B14" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C14" s="15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D14" s="17" t="n">
-        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B14,分行明細!$Q$5:$Q$187,"&lt;"&amp;C14)</f>
-        <v>4</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <f aca="false">D14/$D$16</f>
-        <v>0.0218579234972678</v>
-      </c>
-      <c r="F14" s="17" t="n">
-        <f aca="false">SUM($D$4:D14)</f>
-        <v>180</v>
-      </c>
-      <c r="G14" s="16" t="n">
-        <f aca="false">F14/$D$16</f>
-        <v>0.983606557377049</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="B15" s="15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C15" s="15" t="n">
-        <v>99</v>
-      </c>
-      <c r="D15" s="17" t="n">
-        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B15,分行明細!$Q$5:$Q$187,"&lt;"&amp;C15)</f>
-        <v>3</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <f aca="false">D15/$D$16</f>
-        <v>0.0163934426229508</v>
-      </c>
-      <c r="F15" s="17" t="n">
-        <f aca="false">SUM($D$4:D15)</f>
-        <v>183</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <f aca="false">F15/$D$16</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="18" t="n">
-        <f aca="false">SUM(D4:D15)</f>
-        <v>183</v>
-      </c>
-      <c r="E16" s="20" t="n">
-        <f aca="false">SUM(E4:E15)</f>
-        <v>1</v>
-      </c>
-      <c r="F16" s="18"/>
-      <c r="G16" s="20"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="B19" s="22" t="n">
-        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;=1")</f>
-        <v>99</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="B20" s="22" t="n">
-        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&lt;1")</f>
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="B21" s="22" t="n">
-        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&lt;0.75")</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="B22" s="16" t="n">
-        <f aca="false">MEDIAN(分行明細!$L$5:$L$187)</f>
-        <v>1.01412970723307</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="B23" s="16" t="n">
-        <f aca="false">AVERAGE(分行明細!$L$5:$L$187)</f>
-        <v>1.04641142634779</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="B24" s="16" t="n">
-        <f aca="false">分行明細!K188/分行明細!J188</f>
-        <v>1.05941423772505</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="B25" s="16" t="n">
-        <f aca="false">MIN(分行明細!$L$5:$L$187)</f>
-        <v>0.52210998245614</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="B26" s="16" t="n">
-        <f aca="false">MAX(分行明細!$L$5:$L$187)</f>
-        <v>2.14480437198421</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="C29" s="17" t="n">
-        <f aca="false">COUNTIFS(分行明細!$F$5:$F$187,A29)</f>
-        <v>3</v>
-      </c>
-      <c r="D29" s="16" t="n">
-        <f aca="false">C29/$C$35</f>
-        <v>0.0163934426229508</v>
-      </c>
-      <c r="E29" s="23" t="n">
-        <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$F$5:$F$187,A29)</f>
-        <v>158210000</v>
-      </c>
-      <c r="F29" s="23" t="n">
-        <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$F$5:$F$187,A29)</f>
-        <v>316295495</v>
-      </c>
-      <c r="G29" s="16" t="n">
-        <f aca="false">IFERROR(F29/E29,0)</f>
-        <v>1.99921303963087</v>
-      </c>
-      <c r="H29" s="23" t="n">
-        <f aca="false">F29-E29</f>
-        <v>158085495</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="C30" s="17" t="n">
-        <f aca="false">COUNTIFS(分行明細!$F$5:$F$187,A30)</f>
-        <v>4</v>
-      </c>
-      <c r="D30" s="16" t="n">
-        <f aca="false">C30/$C$35</f>
-        <v>0.0218579234972678</v>
-      </c>
-      <c r="E30" s="23" t="n">
-        <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$F$5:$F$187,A30)</f>
-        <v>380440000</v>
-      </c>
-      <c r="F30" s="23" t="n">
-        <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$F$5:$F$187,A30)</f>
-        <v>600480024</v>
-      </c>
-      <c r="G30" s="16" t="n">
-        <f aca="false">IFERROR(F30/E30,0)</f>
-        <v>1.57838298811902</v>
-      </c>
-      <c r="H30" s="23" t="n">
-        <f aca="false">F30-E30</f>
-        <v>220040024</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="C31" s="17" t="n">
-        <f aca="false">COUNTIFS(分行明細!$F$5:$F$187,A31)</f>
-        <v>40</v>
-      </c>
-      <c r="D31" s="16" t="n">
-        <f aca="false">C31/$C$35</f>
-        <v>0.218579234972678</v>
-      </c>
-      <c r="E31" s="23" t="n">
-        <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$F$5:$F$187,A31)</f>
-        <v>2651530000</v>
-      </c>
-      <c r="F31" s="23" t="n">
-        <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$F$5:$F$187,A31)</f>
-        <v>3438229593</v>
-      </c>
-      <c r="G31" s="16" t="n">
-        <f aca="false">IFERROR(F31/E31,0)</f>
-        <v>1.29669647071691</v>
-      </c>
-      <c r="H31" s="23" t="n">
-        <f aca="false">F31-E31</f>
-        <v>786699593</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="C32" s="17" t="n">
-        <f aca="false">COUNTIFS(分行明細!$F$5:$F$187,A32)</f>
-        <v>52</v>
-      </c>
-      <c r="D32" s="16" t="n">
-        <f aca="false">C32/$C$35</f>
-        <v>0.284153005464481</v>
-      </c>
-      <c r="E32" s="23" t="n">
-        <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$F$5:$F$187,A32)</f>
-        <v>3589010000</v>
-      </c>
-      <c r="F32" s="23" t="n">
-        <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$F$5:$F$187,A32)</f>
-        <v>3947351530</v>
-      </c>
-      <c r="G32" s="16" t="n">
-        <f aca="false">IFERROR(F32/E32,0)</f>
-        <v>1.0998441157868</v>
-      </c>
-      <c r="H32" s="23" t="n">
-        <f aca="false">F32-E32</f>
-        <v>358341530</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="C33" s="17" t="n">
-        <f aca="false">COUNTIFS(分行明細!$F$5:$F$187,A33)</f>
-        <v>65</v>
-      </c>
-      <c r="D33" s="16" t="n">
-        <f aca="false">C33/$C$35</f>
-        <v>0.355191256830601</v>
-      </c>
-      <c r="E33" s="23" t="n">
-        <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$F$5:$F$187,A33)</f>
-        <v>3908460000</v>
-      </c>
-      <c r="F33" s="23" t="n">
-        <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$F$5:$F$187,A33)</f>
-        <v>3432135424</v>
-      </c>
-      <c r="G33" s="16" t="n">
-        <f aca="false">IFERROR(F33/E33,0)</f>
-        <v>0.878129857795654</v>
-      </c>
-      <c r="H33" s="23" t="n">
-        <f aca="false">F33-E33</f>
-        <v>-476324576</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="C34" s="17" t="n">
-        <f aca="false">COUNTIFS(分行明細!$F$5:$F$187,A34)</f>
-        <v>19</v>
-      </c>
-      <c r="D34" s="16" t="n">
-        <f aca="false">C34/$C$35</f>
-        <v>0.103825136612022</v>
-      </c>
-      <c r="E34" s="23" t="n">
-        <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$F$5:$F$187,A34)</f>
-        <v>1097730000</v>
-      </c>
-      <c r="F34" s="23" t="n">
-        <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$F$5:$F$187,A34)</f>
-        <v>751107303</v>
-      </c>
-      <c r="G34" s="16" t="n">
-        <f aca="false">IFERROR(F34/E34,0)</f>
-        <v>0.684236836927113</v>
-      </c>
-      <c r="H34" s="23" t="n">
-        <f aca="false">F34-E34</f>
-        <v>-346622697</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18" t="n">
-        <f aca="false">SUM(C29:C34)</f>
-        <v>183</v>
-      </c>
-      <c r="D35" s="20" t="n">
-        <f aca="false">SUM(D29:D34)</f>
-        <v>1</v>
-      </c>
-      <c r="E35" s="24" t="n">
-        <f aca="false">SUM(E29:E34)</f>
-        <v>11785380000</v>
-      </c>
-      <c r="F35" s="24" t="n">
-        <f aca="false">SUM(F29:F34)</f>
-        <v>12485599369</v>
-      </c>
-      <c r="G35" s="20" t="n">
-        <f aca="false">F35/E35</f>
-        <v>1.05941423772505</v>
-      </c>
-      <c r="H35" s="24" t="n">
-        <f aca="false">SUM(H29:H34)</f>
-        <v>700219369</v>
       </c>
     </row>
   </sheetData>
@@ -17373,6 +17582,725 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B4,分行明細!$Q$5:$Q$187,"&lt;"&amp;C4)</f>
+        <v>2</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <f aca="false">D4/$D$16</f>
+        <v>0.0109289617486339</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <f aca="false">SUM($D$4:D4)</f>
+        <v>2</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <f aca="false">F4/$D$16</f>
+        <v>0.0109289617486339</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B5,分行明細!$Q$5:$Q$187,"&lt;"&amp;C5)</f>
+        <v>7</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <f aca="false">D5/$D$16</f>
+        <v>0.0382513661202186</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <f aca="false">SUM($D$4:D5)</f>
+        <v>9</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <f aca="false">F5/$D$16</f>
+        <v>0.0491803278688525</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="B6" s="25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B6,分行明細!$Q$5:$Q$187,"&lt;"&amp;C6)</f>
+        <v>10</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <f aca="false">D6/$D$16</f>
+        <v>0.0546448087431694</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <f aca="false">SUM($D$4:D6)</f>
+        <v>19</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <f aca="false">F6/$D$16</f>
+        <v>0.103825136612022</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" s="25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B7,分行明細!$Q$5:$Q$187,"&lt;"&amp;C7)</f>
+        <v>12</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <f aca="false">D7/$D$16</f>
+        <v>0.0655737704918033</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <f aca="false">SUM($D$4:D7)</f>
+        <v>31</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <f aca="false">F7/$D$16</f>
+        <v>0.169398907103825</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="B8" s="25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B8,分行明細!$Q$5:$Q$187,"&lt;"&amp;C8)</f>
+        <v>24</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <f aca="false">D8/$D$16</f>
+        <v>0.131147540983607</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <f aca="false">SUM($D$4:D8)</f>
+        <v>55</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <f aca="false">F8/$D$16</f>
+        <v>0.300546448087432</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="B9" s="25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B9,分行明細!$Q$5:$Q$187,"&lt;"&amp;C9)</f>
+        <v>29</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <f aca="false">D9/$D$16</f>
+        <v>0.158469945355191</v>
+      </c>
+      <c r="F9" s="26" t="n">
+        <f aca="false">SUM($D$4:D9)</f>
+        <v>84</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <f aca="false">F9/$D$16</f>
+        <v>0.459016393442623</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B10,分行明細!$Q$5:$Q$187,"&lt;"&amp;C10)</f>
+        <v>25</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <f aca="false">D10/$D$16</f>
+        <v>0.136612021857924</v>
+      </c>
+      <c r="F10" s="26" t="n">
+        <f aca="false">SUM($D$4:D10)</f>
+        <v>109</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <f aca="false">F10/$D$16</f>
+        <v>0.595628415300546</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="B11" s="25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B11,分行明細!$Q$5:$Q$187,"&lt;"&amp;C11)</f>
+        <v>27</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <f aca="false">D11/$D$16</f>
+        <v>0.147540983606557</v>
+      </c>
+      <c r="F11" s="26" t="n">
+        <f aca="false">SUM($D$4:D11)</f>
+        <v>136</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <f aca="false">F11/$D$16</f>
+        <v>0.743169398907104</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B12,分行明細!$Q$5:$Q$187,"&lt;"&amp;C12)</f>
+        <v>17</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <f aca="false">D12/$D$16</f>
+        <v>0.092896174863388</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <f aca="false">SUM($D$4:D12)</f>
+        <v>153</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <f aca="false">F12/$D$16</f>
+        <v>0.836065573770492</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" s="25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B13,分行明細!$Q$5:$Q$187,"&lt;"&amp;C13)</f>
+        <v>23</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <f aca="false">D13/$D$16</f>
+        <v>0.12568306010929</v>
+      </c>
+      <c r="F13" s="26" t="n">
+        <f aca="false">SUM($D$4:D13)</f>
+        <v>176</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <f aca="false">F13/$D$16</f>
+        <v>0.961748633879781</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="B14" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B14,分行明細!$Q$5:$Q$187,"&lt;"&amp;C14)</f>
+        <v>4</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <f aca="false">D14/$D$16</f>
+        <v>0.0218579234972678</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <f aca="false">SUM($D$4:D14)</f>
+        <v>180</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <f aca="false">F14/$D$16</f>
+        <v>0.983606557377049</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="B15" s="25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>99</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;="&amp;B15,分行明細!$Q$5:$Q$187,"&lt;"&amp;C15)</f>
+        <v>3</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <f aca="false">D15/$D$16</f>
+        <v>0.0163934426229508</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <f aca="false">SUM($D$4:D15)</f>
+        <v>183</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <f aca="false">F15/$D$16</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="17" t="n">
+        <f aca="false">SUM(D4:D15)</f>
+        <v>183</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <f aca="false">SUM(E4:E15)</f>
+        <v>1</v>
+      </c>
+      <c r="F16" s="17"/>
+      <c r="G16" s="19"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="B19" s="28" t="n">
+        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&gt;=1")</f>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="B20" s="28" t="n">
+        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&lt;1")</f>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B21" s="28" t="n">
+        <f aca="false">COUNTIFS(分行明細!$Q$5:$Q$187,"&lt;0.75")</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="B22" s="16" t="n">
+        <f aca="false">MEDIAN(分行明細!$L$5:$L$187)</f>
+        <v>1.01412970723307</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="B23" s="16" t="n">
+        <f aca="false">AVERAGE(分行明細!$L$5:$L$187)</f>
+        <v>1.04641142634779</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="B24" s="16" t="n">
+        <f aca="false">分行明細!K188/分行明細!J188</f>
+        <v>1.05941423772505</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="B25" s="16" t="n">
+        <f aca="false">MIN(分行明細!$L$5:$L$187)</f>
+        <v>0.52210998245614</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="B26" s="16" t="n">
+        <f aca="false">MAX(分行明細!$L$5:$L$187)</f>
+        <v>2.14480437198421</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="C29" s="26" t="n">
+        <f aca="false">COUNTIFS(分行明細!$F$5:$F$187,A29)</f>
+        <v>3</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <f aca="false">C29/$C$35</f>
+        <v>0.0163934426229508</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$F$5:$F$187,A29)</f>
+        <v>158210000</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$F$5:$F$187,A29)</f>
+        <v>316295495</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <f aca="false">IFERROR(F29/E29,0)</f>
+        <v>1.99921303963087</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <f aca="false">F29-E29</f>
+        <v>158085495</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="C30" s="26" t="n">
+        <f aca="false">COUNTIFS(分行明細!$F$5:$F$187,A30)</f>
+        <v>4</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <f aca="false">C30/$C$35</f>
+        <v>0.0218579234972678</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$F$5:$F$187,A30)</f>
+        <v>380440000</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$F$5:$F$187,A30)</f>
+        <v>600480024</v>
+      </c>
+      <c r="G30" s="16" t="n">
+        <f aca="false">IFERROR(F30/E30,0)</f>
+        <v>1.57838298811902</v>
+      </c>
+      <c r="H30" s="15" t="n">
+        <f aca="false">F30-E30</f>
+        <v>220040024</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="C31" s="26" t="n">
+        <f aca="false">COUNTIFS(分行明細!$F$5:$F$187,A31)</f>
+        <v>40</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <f aca="false">C31/$C$35</f>
+        <v>0.218579234972678</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$F$5:$F$187,A31)</f>
+        <v>2651530000</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$F$5:$F$187,A31)</f>
+        <v>3438229593</v>
+      </c>
+      <c r="G31" s="16" t="n">
+        <f aca="false">IFERROR(F31/E31,0)</f>
+        <v>1.29669647071691</v>
+      </c>
+      <c r="H31" s="15" t="n">
+        <f aca="false">F31-E31</f>
+        <v>786699593</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="C32" s="26" t="n">
+        <f aca="false">COUNTIFS(分行明細!$F$5:$F$187,A32)</f>
+        <v>52</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <f aca="false">C32/$C$35</f>
+        <v>0.284153005464481</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$F$5:$F$187,A32)</f>
+        <v>3589010000</v>
+      </c>
+      <c r="F32" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$F$5:$F$187,A32)</f>
+        <v>3947351530</v>
+      </c>
+      <c r="G32" s="16" t="n">
+        <f aca="false">IFERROR(F32/E32,0)</f>
+        <v>1.0998441157868</v>
+      </c>
+      <c r="H32" s="15" t="n">
+        <f aca="false">F32-E32</f>
+        <v>358341530</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="C33" s="26" t="n">
+        <f aca="false">COUNTIFS(分行明細!$F$5:$F$187,A33)</f>
+        <v>65</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <f aca="false">C33/$C$35</f>
+        <v>0.355191256830601</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$F$5:$F$187,A33)</f>
+        <v>3908460000</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$F$5:$F$187,A33)</f>
+        <v>3432135424</v>
+      </c>
+      <c r="G33" s="16" t="n">
+        <f aca="false">IFERROR(F33/E33,0)</f>
+        <v>0.878129857795654</v>
+      </c>
+      <c r="H33" s="15" t="n">
+        <f aca="false">F33-E33</f>
+        <v>-476324576</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="C34" s="26" t="n">
+        <f aca="false">COUNTIFS(分行明細!$F$5:$F$187,A34)</f>
+        <v>19</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <f aca="false">C34/$C$35</f>
+        <v>0.103825136612022</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$F$5:$F$187,A34)</f>
+        <v>1097730000</v>
+      </c>
+      <c r="F34" s="15" t="n">
+        <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$F$5:$F$187,A34)</f>
+        <v>751107303</v>
+      </c>
+      <c r="G34" s="16" t="n">
+        <f aca="false">IFERROR(F34/E34,0)</f>
+        <v>0.684236836927113</v>
+      </c>
+      <c r="H34" s="15" t="n">
+        <f aca="false">F34-E34</f>
+        <v>-346622697</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17" t="n">
+        <f aca="false">SUM(C29:C34)</f>
+        <v>183</v>
+      </c>
+      <c r="D35" s="19" t="n">
+        <f aca="false">SUM(D29:D34)</f>
+        <v>1</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <f aca="false">SUM(E29:E34)</f>
+        <v>11785380000</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <f aca="false">SUM(F29:F34)</f>
+        <v>12485599369</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <f aca="false">F35/E35</f>
+        <v>1.05941423772505</v>
+      </c>
+      <c r="H35" s="18" t="n">
+        <f aca="false">SUM(H29:H34)</f>
+        <v>700219369</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -17395,26 +18323,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>9</v>
@@ -17426,7 +18354,7 @@
         <v>12</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>14</v>
@@ -17435,50 +18363,50 @@
         <v>15</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>268</v>
+      <c r="B5" s="26" t="s">
+        <v>282</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="D5" s="17" t="n">
+        <v>283</v>
+      </c>
+      <c r="D5" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A5)</f>
         <v>3</v>
       </c>
-      <c r="E5" s="23" t="n">
+      <c r="E5" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$H$5:$H$187,分行明細!$E$5:$E$187,A5)</f>
         <v>140411824</v>
       </c>
-      <c r="F5" s="23" t="n">
+      <c r="F5" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$E$5:$E$187,A5)</f>
         <v>105120000</v>
       </c>
-      <c r="G5" s="23" t="n">
+      <c r="G5" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$E$5:$E$187,A5)</f>
         <v>198394389</v>
       </c>
@@ -17490,31 +18418,31 @@
         <f aca="false">IFERROR(F5/E5-1,0)</f>
         <v>-0.251345100395534</v>
       </c>
-      <c r="J5" s="23" t="n">
+      <c r="J5" s="15" t="n">
         <f aca="false">G5-F5</f>
         <v>93274389</v>
       </c>
-      <c r="K5" s="23" t="n">
+      <c r="K5" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$O$5:$O$187,分行明細!$E$5:$E$187,A5)</f>
         <v>95405767</v>
       </c>
-      <c r="L5" s="23" t="n">
+      <c r="L5" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$P$5:$P$187,分行明細!$E$5:$E$187,A5)</f>
         <v>-2131378</v>
       </c>
-      <c r="M5" s="17" t="n">
+      <c r="M5" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A5,分行明細!$N$5:$N$187,"&gt;=0")</f>
         <v>2</v>
       </c>
-      <c r="N5" s="17" t="n">
+      <c r="N5" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A5,分行明細!$N$5:$N$187,"&lt;0")</f>
         <v>1</v>
       </c>
-      <c r="O5" s="17" t="n">
+      <c r="O5" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A5,分行明細!$F$5:$F$187,"TYPE_5")+COUNTIFS(分行明細!$E$5:$E$187,A5,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>1</v>
       </c>
-      <c r="P5" s="17" t="n">
+      <c r="P5" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A5,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>0</v>
       </c>
@@ -17524,28 +18452,28 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>270</v>
+      <c r="B6" s="26" t="s">
+        <v>284</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="D6" s="17" t="n">
+        <v>285</v>
+      </c>
+      <c r="D6" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A6)</f>
         <v>5</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$H$5:$H$187,分行明細!$E$5:$E$187,A6)</f>
         <v>318550006</v>
       </c>
-      <c r="F6" s="23" t="n">
+      <c r="F6" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$E$5:$E$187,A6)</f>
         <v>260640000</v>
       </c>
-      <c r="G6" s="23" t="n">
+      <c r="G6" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$E$5:$E$187,A6)</f>
         <v>334547528</v>
       </c>
@@ -17557,31 +18485,31 @@
         <f aca="false">IFERROR(F6/E6-1,0)</f>
         <v>-0.181792512664401</v>
       </c>
-      <c r="J6" s="23" t="n">
+      <c r="J6" s="15" t="n">
         <f aca="false">G6-F6</f>
         <v>73907528</v>
       </c>
-      <c r="K6" s="23" t="n">
+      <c r="K6" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$O$5:$O$187,分行明細!$E$5:$E$187,A6)</f>
         <v>88003176</v>
       </c>
-      <c r="L6" s="23" t="n">
+      <c r="L6" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$P$5:$P$187,分行明細!$E$5:$E$187,A6)</f>
         <v>-14095648</v>
       </c>
-      <c r="M6" s="17" t="n">
+      <c r="M6" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A6,分行明細!$N$5:$N$187,"&gt;=0")</f>
         <v>3</v>
       </c>
-      <c r="N6" s="17" t="n">
+      <c r="N6" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A6,分行明細!$N$5:$N$187,"&lt;0")</f>
         <v>2</v>
       </c>
-      <c r="O6" s="17" t="n">
+      <c r="O6" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A6,分行明細!$F$5:$F$187,"TYPE_5")+COUNTIFS(分行明細!$E$5:$E$187,A6,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>2</v>
       </c>
-      <c r="P6" s="17" t="n">
+      <c r="P6" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A6,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>0</v>
       </c>
@@ -17591,28 +18519,28 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>272</v>
+      <c r="B7" s="26" t="s">
+        <v>286</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>273</v>
-      </c>
-      <c r="D7" s="17" t="n">
+        <v>287</v>
+      </c>
+      <c r="D7" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A7)</f>
         <v>11</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$H$5:$H$187,分行明細!$E$5:$E$187,A7)</f>
         <v>863954080</v>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$E$5:$E$187,A7)</f>
         <v>804480000</v>
       </c>
-      <c r="G7" s="23" t="n">
+      <c r="G7" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$E$5:$E$187,A7)</f>
         <v>996943084</v>
       </c>
@@ -17624,31 +18552,31 @@
         <f aca="false">IFERROR(F7/E7-1,0)</f>
         <v>-0.06883939942734</v>
       </c>
-      <c r="J7" s="23" t="n">
+      <c r="J7" s="15" t="n">
         <f aca="false">G7-F7</f>
         <v>192463084</v>
       </c>
-      <c r="K7" s="23" t="n">
+      <c r="K7" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$O$5:$O$187,分行明細!$E$5:$E$187,A7)</f>
         <v>192463084</v>
       </c>
-      <c r="L7" s="23" t="n">
+      <c r="L7" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$P$5:$P$187,分行明細!$E$5:$E$187,A7)</f>
         <v>0</v>
       </c>
-      <c r="M7" s="17" t="n">
+      <c r="M7" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A7,分行明細!$N$5:$N$187,"&gt;=0")</f>
         <v>11</v>
       </c>
-      <c r="N7" s="17" t="n">
+      <c r="N7" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A7,分行明細!$N$5:$N$187,"&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="O7" s="17" t="n">
+      <c r="O7" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A7,分行明細!$F$5:$F$187,"TYPE_5")+COUNTIFS(分行明細!$E$5:$E$187,A7,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>0</v>
       </c>
-      <c r="P7" s="17" t="n">
+      <c r="P7" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A7,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>0</v>
       </c>
@@ -17658,28 +18586,28 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>274</v>
+      <c r="B8" s="26" t="s">
+        <v>288</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>275</v>
-      </c>
-      <c r="D8" s="17" t="n">
+        <v>289</v>
+      </c>
+      <c r="D8" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A8)</f>
         <v>6</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$H$5:$H$187,分行明細!$E$5:$E$187,A8)</f>
         <v>534730685</v>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F8" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$E$5:$E$187,A8)</f>
         <v>531970000</v>
       </c>
-      <c r="G8" s="23" t="n">
+      <c r="G8" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$E$5:$E$187,A8)</f>
         <v>693732166</v>
       </c>
@@ -17691,31 +18619,31 @@
         <f aca="false">IFERROR(F8/E8-1,0)</f>
         <v>-0.00516275777216713</v>
       </c>
-      <c r="J8" s="23" t="n">
+      <c r="J8" s="15" t="n">
         <f aca="false">G8-F8</f>
         <v>161762166</v>
       </c>
-      <c r="K8" s="23" t="n">
+      <c r="K8" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$O$5:$O$187,分行明細!$E$5:$E$187,A8)</f>
         <v>164754047</v>
       </c>
-      <c r="L8" s="23" t="n">
+      <c r="L8" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$P$5:$P$187,分行明細!$E$5:$E$187,A8)</f>
         <v>-2991881</v>
       </c>
-      <c r="M8" s="17" t="n">
+      <c r="M8" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A8,分行明細!$N$5:$N$187,"&gt;=0")</f>
         <v>5</v>
       </c>
-      <c r="N8" s="17" t="n">
+      <c r="N8" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A8,分行明細!$N$5:$N$187,"&lt;0")</f>
         <v>1</v>
       </c>
-      <c r="O8" s="17" t="n">
+      <c r="O8" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A8,分行明細!$F$5:$F$187,"TYPE_5")+COUNTIFS(分行明細!$E$5:$E$187,A8,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>1</v>
       </c>
-      <c r="P8" s="17" t="n">
+      <c r="P8" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A8,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>0</v>
       </c>
@@ -17725,28 +18653,28 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>276</v>
+      <c r="B9" s="26" t="s">
+        <v>290</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="D9" s="17" t="n">
+        <v>291</v>
+      </c>
+      <c r="D9" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A9)</f>
         <v>25</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$H$5:$H$187,分行明細!$E$5:$E$187,A9)</f>
         <v>1603285600</v>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F9" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$E$5:$E$187,A9)</f>
         <v>1731760000</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G9" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$E$5:$E$187,A9)</f>
         <v>1939518684</v>
       </c>
@@ -17758,31 +18686,31 @@
         <f aca="false">IFERROR(F9/E9-1,0)</f>
         <v>0.0801319490426409</v>
       </c>
-      <c r="J9" s="23" t="n">
+      <c r="J9" s="15" t="n">
         <f aca="false">G9-F9</f>
         <v>207758684</v>
       </c>
-      <c r="K9" s="23" t="n">
+      <c r="K9" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$O$5:$O$187,分行明細!$E$5:$E$187,A9)</f>
         <v>236460620</v>
       </c>
-      <c r="L9" s="23" t="n">
+      <c r="L9" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$P$5:$P$187,分行明細!$E$5:$E$187,A9)</f>
         <v>-28701936</v>
       </c>
-      <c r="M9" s="17" t="n">
+      <c r="M9" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A9,分行明細!$N$5:$N$187,"&gt;=0")</f>
         <v>20</v>
       </c>
-      <c r="N9" s="17" t="n">
+      <c r="N9" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A9,分行明細!$N$5:$N$187,"&lt;0")</f>
         <v>5</v>
       </c>
-      <c r="O9" s="17" t="n">
+      <c r="O9" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A9,分行明細!$F$5:$F$187,"TYPE_5")+COUNTIFS(分行明細!$E$5:$E$187,A9,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>5</v>
       </c>
-      <c r="P9" s="17" t="n">
+      <c r="P9" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A9,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>0</v>
       </c>
@@ -17792,28 +18720,28 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>278</v>
+      <c r="B10" s="26" t="s">
+        <v>292</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>279</v>
-      </c>
-      <c r="D10" s="17" t="n">
+        <v>293</v>
+      </c>
+      <c r="D10" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A10)</f>
         <v>20</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$H$5:$H$187,分行明細!$E$5:$E$187,A10)</f>
         <v>1175703816</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$E$5:$E$187,A10)</f>
         <v>1305460000</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$E$5:$E$187,A10)</f>
         <v>1371146437</v>
       </c>
@@ -17825,31 +18753,31 @@
         <f aca="false">IFERROR(F10/E10-1,0)</f>
         <v>0.110364687291276</v>
       </c>
-      <c r="J10" s="23" t="n">
+      <c r="J10" s="15" t="n">
         <f aca="false">G10-F10</f>
         <v>65686437</v>
       </c>
-      <c r="K10" s="23" t="n">
+      <c r="K10" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$O$5:$O$187,分行明細!$E$5:$E$187,A10)</f>
         <v>130455738</v>
       </c>
-      <c r="L10" s="23" t="n">
+      <c r="L10" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$P$5:$P$187,分行明細!$E$5:$E$187,A10)</f>
         <v>-64769301</v>
       </c>
-      <c r="M10" s="17" t="n">
+      <c r="M10" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A10,分行明細!$N$5:$N$187,"&gt;=0")</f>
         <v>11</v>
       </c>
-      <c r="N10" s="17" t="n">
+      <c r="N10" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A10,分行明細!$N$5:$N$187,"&lt;0")</f>
         <v>9</v>
       </c>
-      <c r="O10" s="17" t="n">
+      <c r="O10" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A10,分行明細!$F$5:$F$187,"TYPE_5")+COUNTIFS(分行明細!$E$5:$E$187,A10,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>9</v>
       </c>
-      <c r="P10" s="17" t="n">
+      <c r="P10" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A10,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>0</v>
       </c>
@@ -17859,28 +18787,28 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>280</v>
+      <c r="B11" s="26" t="s">
+        <v>294</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="D11" s="17" t="n">
+        <v>295</v>
+      </c>
+      <c r="D11" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A11)</f>
         <v>36</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$H$5:$H$187,分行明細!$E$5:$E$187,A11)</f>
         <v>1766590632</v>
       </c>
-      <c r="F11" s="23" t="n">
+      <c r="F11" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$E$5:$E$187,A11)</f>
         <v>2151820000</v>
       </c>
-      <c r="G11" s="23" t="n">
+      <c r="G11" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$E$5:$E$187,A11)</f>
         <v>2282804453</v>
       </c>
@@ -17892,31 +18820,31 @@
         <f aca="false">IFERROR(F11/E11-1,0)</f>
         <v>0.218063744379688</v>
       </c>
-      <c r="J11" s="23" t="n">
+      <c r="J11" s="15" t="n">
         <f aca="false">G11-F11</f>
         <v>130984453</v>
       </c>
-      <c r="K11" s="23" t="n">
+      <c r="K11" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$O$5:$O$187,分行明細!$E$5:$E$187,A11)</f>
         <v>280304068</v>
       </c>
-      <c r="L11" s="23" t="n">
+      <c r="L11" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$P$5:$P$187,分行明細!$E$5:$E$187,A11)</f>
         <v>-149319615</v>
       </c>
-      <c r="M11" s="17" t="n">
+      <c r="M11" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A11,分行明細!$N$5:$N$187,"&gt;=0")</f>
         <v>20</v>
       </c>
-      <c r="N11" s="17" t="n">
+      <c r="N11" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A11,分行明細!$N$5:$N$187,"&lt;0")</f>
         <v>16</v>
       </c>
-      <c r="O11" s="17" t="n">
+      <c r="O11" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A11,分行明細!$F$5:$F$187,"TYPE_5")+COUNTIFS(分行明細!$E$5:$E$187,A11,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>16</v>
       </c>
-      <c r="P11" s="17" t="n">
+      <c r="P11" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A11,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>3</v>
       </c>
@@ -17926,28 +18854,28 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="17" t="s">
-        <v>282</v>
+      <c r="B12" s="26" t="s">
+        <v>296</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="D12" s="17" t="n">
+        <v>297</v>
+      </c>
+      <c r="D12" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A12)</f>
         <v>53</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$H$5:$H$187,分行明細!$E$5:$E$187,A12)</f>
         <v>2361091197</v>
       </c>
-      <c r="F12" s="23" t="n">
+      <c r="F12" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$E$5:$E$187,A12)</f>
         <v>3359170000</v>
       </c>
-      <c r="G12" s="23" t="n">
+      <c r="G12" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$E$5:$E$187,A12)</f>
         <v>3216095440</v>
       </c>
@@ -17959,31 +18887,31 @@
         <f aca="false">IFERROR(F12/E12-1,0)</f>
         <v>0.422719293633451</v>
       </c>
-      <c r="J12" s="23" t="n">
+      <c r="J12" s="15" t="n">
         <f aca="false">G12-F12</f>
         <v>-143074560</v>
       </c>
-      <c r="K12" s="23" t="n">
+      <c r="K12" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$O$5:$O$187,分行明細!$E$5:$E$187,A12)</f>
         <v>199557239</v>
       </c>
-      <c r="L12" s="23" t="n">
+      <c r="L12" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$P$5:$P$187,分行明細!$E$5:$E$187,A12)</f>
         <v>-342631799</v>
       </c>
-      <c r="M12" s="17" t="n">
+      <c r="M12" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A12,分行明細!$N$5:$N$187,"&gt;=0")</f>
         <v>21</v>
       </c>
-      <c r="N12" s="17" t="n">
+      <c r="N12" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A12,分行明細!$N$5:$N$187,"&lt;0")</f>
         <v>32</v>
       </c>
-      <c r="O12" s="17" t="n">
+      <c r="O12" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A12,分行明細!$F$5:$F$187,"TYPE_5")+COUNTIFS(分行明細!$E$5:$E$187,A12,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>32</v>
       </c>
-      <c r="P12" s="17" t="n">
+      <c r="P12" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A12,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>9</v>
       </c>
@@ -17993,28 +18921,28 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="26" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="D13" s="17" t="n">
+        <v>298</v>
+      </c>
+      <c r="D13" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A13)</f>
         <v>24</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$H$5:$H$187,分行明細!$E$5:$E$187,A13)</f>
         <v>865274321</v>
       </c>
-      <c r="F13" s="23" t="n">
+      <c r="F13" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$E$5:$E$187,A13)</f>
         <v>1534960000</v>
       </c>
-      <c r="G13" s="23" t="n">
+      <c r="G13" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$E$5:$E$187,A13)</f>
         <v>1452417188</v>
       </c>
@@ -18026,31 +18954,31 @@
         <f aca="false">IFERROR(F13/E13-1,0)</f>
         <v>0.773957648744322</v>
       </c>
-      <c r="J13" s="23" t="n">
+      <c r="J13" s="15" t="n">
         <f aca="false">G13-F13</f>
         <v>-82542812</v>
       </c>
-      <c r="K13" s="23" t="n">
+      <c r="K13" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$O$5:$O$187,分行明細!$E$5:$E$187,A13)</f>
         <v>135762903</v>
       </c>
-      <c r="L13" s="23" t="n">
+      <c r="L13" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$P$5:$P$187,分行明細!$E$5:$E$187,A13)</f>
         <v>-218305715</v>
       </c>
-      <c r="M13" s="17" t="n">
+      <c r="M13" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A13,分行明細!$N$5:$N$187,"&gt;=0")</f>
         <v>6</v>
       </c>
-      <c r="N13" s="17" t="n">
+      <c r="N13" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A13,分行明細!$N$5:$N$187,"&lt;0")</f>
         <v>18</v>
       </c>
-      <c r="O13" s="17" t="n">
+      <c r="O13" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A13,分行明細!$F$5:$F$187,"TYPE_5")+COUNTIFS(分行明細!$E$5:$E$187,A13,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>18</v>
       </c>
-      <c r="P13" s="17" t="n">
+      <c r="P13" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,A13,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>7</v>
       </c>
@@ -18060,190 +18988,190 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>285</v>
-      </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18" t="n">
+      <c r="A14" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17" t="n">
         <f aca="false">SUM(D5:D10)</f>
         <v>70</v>
       </c>
-      <c r="E14" s="24" t="n">
+      <c r="E14" s="18" t="n">
         <f aca="false">SUM(E5:E10)</f>
         <v>4636636011</v>
       </c>
-      <c r="F14" s="24" t="n">
+      <c r="F14" s="18" t="n">
         <f aca="false">SUM(F5:F10)</f>
         <v>4739430000</v>
       </c>
-      <c r="G14" s="24" t="n">
+      <c r="G14" s="18" t="n">
         <f aca="false">SUM(G5:G10)</f>
         <v>5534282288</v>
       </c>
-      <c r="H14" s="20" t="n">
+      <c r="H14" s="19" t="n">
         <f aca="false">IFERROR(G14/F14,0)</f>
         <v>1.16771052383936</v>
       </c>
-      <c r="I14" s="20" t="n">
+      <c r="I14" s="19" t="n">
         <f aca="false">IFERROR(F14/E14-1,0)</f>
         <v>0.0221699501009203</v>
       </c>
-      <c r="J14" s="24" t="n">
+      <c r="J14" s="18" t="n">
         <f aca="false">SUM(J5:J10)</f>
         <v>794852288</v>
       </c>
-      <c r="K14" s="24" t="n">
+      <c r="K14" s="18" t="n">
         <f aca="false">SUM(K5:K10)</f>
         <v>907542432</v>
       </c>
-      <c r="L14" s="24" t="n">
+      <c r="L14" s="18" t="n">
         <f aca="false">SUM(L5:L10)</f>
         <v>-112690144</v>
       </c>
-      <c r="M14" s="18" t="n">
+      <c r="M14" s="17" t="n">
         <f aca="false">SUM(M5:M10)</f>
         <v>52</v>
       </c>
-      <c r="N14" s="18" t="n">
+      <c r="N14" s="17" t="n">
         <f aca="false">SUM(N5:N10)</f>
         <v>18</v>
       </c>
-      <c r="O14" s="18" t="n">
+      <c r="O14" s="17" t="n">
         <f aca="false">SUM(O5:O10)</f>
         <v>18</v>
       </c>
-      <c r="P14" s="18" t="n">
+      <c r="P14" s="17" t="n">
         <f aca="false">SUM(P5:P10)</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="20" t="n">
+      <c r="Q14" s="19" t="n">
         <f aca="false">IFERROR(P14/D14,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>286</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18" t="n">
+      <c r="A15" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17" t="n">
         <f aca="false">SUM(D11:D13)</f>
         <v>113</v>
       </c>
-      <c r="E15" s="24" t="n">
+      <c r="E15" s="18" t="n">
         <f aca="false">SUM(E11:E13)</f>
         <v>4992956150</v>
       </c>
-      <c r="F15" s="24" t="n">
+      <c r="F15" s="18" t="n">
         <f aca="false">SUM(F11:F13)</f>
         <v>7045950000</v>
       </c>
-      <c r="G15" s="24" t="n">
+      <c r="G15" s="18" t="n">
         <f aca="false">SUM(G11:G13)</f>
         <v>6951317081</v>
       </c>
-      <c r="H15" s="20" t="n">
+      <c r="H15" s="19" t="n">
         <f aca="false">IFERROR(G15/F15,0)</f>
         <v>0.986569175341863</v>
       </c>
-      <c r="I15" s="20" t="n">
+      <c r="I15" s="19" t="n">
         <f aca="false">IFERROR(F15/E15-1,0)</f>
         <v>0.411178025266655</v>
       </c>
-      <c r="J15" s="24" t="n">
+      <c r="J15" s="18" t="n">
         <f aca="false">SUM(J11:J13)</f>
         <v>-94632919</v>
       </c>
-      <c r="K15" s="24" t="n">
+      <c r="K15" s="18" t="n">
         <f aca="false">SUM(K11:K13)</f>
         <v>615624210</v>
       </c>
-      <c r="L15" s="24" t="n">
+      <c r="L15" s="18" t="n">
         <f aca="false">SUM(L11:L13)</f>
         <v>-710257129</v>
       </c>
-      <c r="M15" s="18" t="n">
+      <c r="M15" s="17" t="n">
         <f aca="false">SUM(M11:M13)</f>
         <v>47</v>
       </c>
-      <c r="N15" s="18" t="n">
+      <c r="N15" s="17" t="n">
         <f aca="false">SUM(N11:N13)</f>
         <v>66</v>
       </c>
-      <c r="O15" s="18" t="n">
+      <c r="O15" s="17" t="n">
         <f aca="false">SUM(O11:O13)</f>
         <v>66</v>
       </c>
-      <c r="P15" s="18" t="n">
+      <c r="P15" s="17" t="n">
         <f aca="false">SUM(P11:P13)</f>
         <v>19</v>
       </c>
-      <c r="Q15" s="20" t="n">
+      <c r="Q15" s="19" t="n">
         <f aca="false">IFERROR(P15/D15,0)</f>
         <v>0.168141592920354</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18" t="n">
+      <c r="A16" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17" t="n">
         <f aca="false">SUM(D5:D13)</f>
         <v>183</v>
       </c>
-      <c r="E16" s="24" t="n">
+      <c r="E16" s="18" t="n">
         <f aca="false">SUM(E5:E13)</f>
         <v>9629592161</v>
       </c>
-      <c r="F16" s="24" t="n">
+      <c r="F16" s="18" t="n">
         <f aca="false">SUM(F5:F13)</f>
         <v>11785380000</v>
       </c>
-      <c r="G16" s="24" t="n">
+      <c r="G16" s="18" t="n">
         <f aca="false">SUM(G5:G13)</f>
         <v>12485599369</v>
       </c>
-      <c r="H16" s="20" t="n">
+      <c r="H16" s="19" t="n">
         <f aca="false">IFERROR(G16/F16,0)</f>
         <v>1.05941423772505</v>
       </c>
-      <c r="I16" s="20" t="n">
+      <c r="I16" s="19" t="n">
         <f aca="false">IFERROR(F16/E16-1,0)</f>
         <v>0.223871146665066</v>
       </c>
-      <c r="J16" s="24" t="n">
+      <c r="J16" s="18" t="n">
         <f aca="false">SUM(J5:J13)</f>
         <v>700219369</v>
       </c>
-      <c r="K16" s="24" t="n">
+      <c r="K16" s="18" t="n">
         <f aca="false">SUM(K5:K13)</f>
         <v>1523166642</v>
       </c>
-      <c r="L16" s="24" t="n">
+      <c r="L16" s="18" t="n">
         <f aca="false">SUM(L5:L13)</f>
         <v>-822947273</v>
       </c>
-      <c r="M16" s="18" t="n">
+      <c r="M16" s="17" t="n">
         <f aca="false">SUM(M5:M13)</f>
         <v>99</v>
       </c>
-      <c r="N16" s="18" t="n">
+      <c r="N16" s="17" t="n">
         <f aca="false">SUM(N5:N13)</f>
         <v>84</v>
       </c>
-      <c r="O16" s="18" t="n">
+      <c r="O16" s="17" t="n">
         <f aca="false">SUM(O5:O13)</f>
         <v>84</v>
       </c>
-      <c r="P16" s="18" t="n">
+      <c r="P16" s="17" t="n">
         <f aca="false">SUM(P5:P13)</f>
         <v>19</v>
       </c>
-      <c r="Q16" s="20" t="n">
+      <c r="Q16" s="19" t="n">
         <f aca="false">IFERROR(P16/D16,0)</f>
         <v>0.103825136612022</v>
       </c>
@@ -18259,7 +19187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -18280,98 +19208,98 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D3" s="25" t="s">
-        <v>289</v>
+      <c r="D3" s="20" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>216</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>268</v>
+      <c r="B5" s="26" t="s">
+        <v>282</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="D5" s="26" t="n">
+        <v>283</v>
+      </c>
+      <c r="D5" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A5,分行明細!$F$5:$F$187,"TYPE_1")</f>
         <v>2</v>
       </c>
-      <c r="E5" s="26" t="n">
+      <c r="E5" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A5,分行明細!$F$5:$F$187,"TYPE_2")</f>
         <v>0</v>
       </c>
-      <c r="F5" s="26" t="n">
+      <c r="F5" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A5,分行明細!$F$5:$F$187,"TYPE_3")</f>
         <v>0</v>
       </c>
-      <c r="G5" s="26" t="n">
+      <c r="G5" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A5,分行明細!$F$5:$F$187,"TYPE_4")</f>
         <v>0</v>
       </c>
-      <c r="H5" s="26" t="n">
+      <c r="H5" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A5,分行明細!$F$5:$F$187,"TYPE_5")</f>
         <v>1</v>
       </c>
-      <c r="I5" s="26" t="n">
+      <c r="I5" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A5,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>0</v>
       </c>
-      <c r="J5" s="17" t="n">
+      <c r="J5" s="26" t="n">
         <f aca="false">SUM(D5:I5)</f>
         <v>3</v>
       </c>
-      <c r="K5" s="17" t="n">
+      <c r="K5" s="26" t="n">
         <f aca="false">H5+I5</f>
         <v>1</v>
       </c>
-      <c r="L5" s="17" t="n">
+      <c r="L5" s="26" t="n">
         <f aca="false">I5</f>
         <v>0</v>
       </c>
@@ -18381,48 +19309,48 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>270</v>
+      <c r="B6" s="26" t="s">
+        <v>284</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="D6" s="26" t="n">
+        <v>285</v>
+      </c>
+      <c r="D6" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A6,分行明細!$F$5:$F$187,"TYPE_1")</f>
         <v>1</v>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A6,分行明細!$F$5:$F$187,"TYPE_2")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="26" t="n">
+      <c r="F6" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A6,分行明細!$F$5:$F$187,"TYPE_3")</f>
         <v>1</v>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A6,分行明細!$F$5:$F$187,"TYPE_4")</f>
         <v>1</v>
       </c>
-      <c r="H6" s="26" t="n">
+      <c r="H6" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A6,分行明細!$F$5:$F$187,"TYPE_5")</f>
         <v>2</v>
       </c>
-      <c r="I6" s="26" t="n">
+      <c r="I6" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A6,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>0</v>
       </c>
-      <c r="J6" s="17" t="n">
+      <c r="J6" s="26" t="n">
         <f aca="false">SUM(D6:I6)</f>
         <v>5</v>
       </c>
-      <c r="K6" s="17" t="n">
+      <c r="K6" s="26" t="n">
         <f aca="false">H6+I6</f>
         <v>2</v>
       </c>
-      <c r="L6" s="17" t="n">
+      <c r="L6" s="26" t="n">
         <f aca="false">I6</f>
         <v>0</v>
       </c>
@@ -18432,48 +19360,48 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>272</v>
+      <c r="B7" s="26" t="s">
+        <v>286</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>273</v>
-      </c>
-      <c r="D7" s="26" t="n">
+        <v>287</v>
+      </c>
+      <c r="D7" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A7,分行明細!$F$5:$F$187,"TYPE_1")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="26" t="n">
+      <c r="E7" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A7,分行明細!$F$5:$F$187,"TYPE_2")</f>
         <v>1</v>
       </c>
-      <c r="F7" s="26" t="n">
+      <c r="F7" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A7,分行明細!$F$5:$F$187,"TYPE_3")</f>
         <v>3</v>
       </c>
-      <c r="G7" s="26" t="n">
+      <c r="G7" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A7,分行明細!$F$5:$F$187,"TYPE_4")</f>
         <v>7</v>
       </c>
-      <c r="H7" s="26" t="n">
+      <c r="H7" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A7,分行明細!$F$5:$F$187,"TYPE_5")</f>
         <v>0</v>
       </c>
-      <c r="I7" s="26" t="n">
+      <c r="I7" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A7,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>0</v>
       </c>
-      <c r="J7" s="17" t="n">
+      <c r="J7" s="26" t="n">
         <f aca="false">SUM(D7:I7)</f>
         <v>11</v>
       </c>
-      <c r="K7" s="17" t="n">
+      <c r="K7" s="26" t="n">
         <f aca="false">H7+I7</f>
         <v>0</v>
       </c>
-      <c r="L7" s="17" t="n">
+      <c r="L7" s="26" t="n">
         <f aca="false">I7</f>
         <v>0</v>
       </c>
@@ -18483,48 +19411,48 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>274</v>
+      <c r="B8" s="26" t="s">
+        <v>288</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>275</v>
-      </c>
-      <c r="D8" s="26" t="n">
+        <v>289</v>
+      </c>
+      <c r="D8" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A8,分行明細!$F$5:$F$187,"TYPE_1")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="26" t="n">
+      <c r="E8" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A8,分行明細!$F$5:$F$187,"TYPE_2")</f>
         <v>1</v>
       </c>
-      <c r="F8" s="26" t="n">
+      <c r="F8" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A8,分行明細!$F$5:$F$187,"TYPE_3")</f>
         <v>3</v>
       </c>
-      <c r="G8" s="26" t="n">
+      <c r="G8" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A8,分行明細!$F$5:$F$187,"TYPE_4")</f>
         <v>1</v>
       </c>
-      <c r="H8" s="26" t="n">
+      <c r="H8" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A8,分行明細!$F$5:$F$187,"TYPE_5")</f>
         <v>1</v>
       </c>
-      <c r="I8" s="26" t="n">
+      <c r="I8" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A8,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>0</v>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="26" t="n">
         <f aca="false">SUM(D8:I8)</f>
         <v>6</v>
       </c>
-      <c r="K8" s="17" t="n">
+      <c r="K8" s="26" t="n">
         <f aca="false">H8+I8</f>
         <v>1</v>
       </c>
-      <c r="L8" s="17" t="n">
+      <c r="L8" s="26" t="n">
         <f aca="false">I8</f>
         <v>0</v>
       </c>
@@ -18534,48 +19462,48 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>276</v>
+      <c r="B9" s="26" t="s">
+        <v>290</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="D9" s="26" t="n">
+        <v>291</v>
+      </c>
+      <c r="D9" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A9,分行明細!$F$5:$F$187,"TYPE_1")</f>
         <v>0</v>
       </c>
-      <c r="E9" s="26" t="n">
+      <c r="E9" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A9,分行明細!$F$5:$F$187,"TYPE_2")</f>
         <v>0</v>
       </c>
-      <c r="F9" s="26" t="n">
+      <c r="F9" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A9,分行明細!$F$5:$F$187,"TYPE_3")</f>
         <v>7</v>
       </c>
-      <c r="G9" s="26" t="n">
+      <c r="G9" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A9,分行明細!$F$5:$F$187,"TYPE_4")</f>
         <v>13</v>
       </c>
-      <c r="H9" s="26" t="n">
+      <c r="H9" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A9,分行明細!$F$5:$F$187,"TYPE_5")</f>
         <v>5</v>
       </c>
-      <c r="I9" s="26" t="n">
+      <c r="I9" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A9,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>0</v>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="26" t="n">
         <f aca="false">SUM(D9:I9)</f>
         <v>25</v>
       </c>
-      <c r="K9" s="17" t="n">
+      <c r="K9" s="26" t="n">
         <f aca="false">H9+I9</f>
         <v>5</v>
       </c>
-      <c r="L9" s="17" t="n">
+      <c r="L9" s="26" t="n">
         <f aca="false">I9</f>
         <v>0</v>
       </c>
@@ -18585,48 +19513,48 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>278</v>
+      <c r="B10" s="26" t="s">
+        <v>292</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>279</v>
-      </c>
-      <c r="D10" s="26" t="n">
+        <v>293</v>
+      </c>
+      <c r="D10" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A10,分行明細!$F$5:$F$187,"TYPE_1")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="26" t="n">
+      <c r="E10" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A10,分行明細!$F$5:$F$187,"TYPE_2")</f>
         <v>0</v>
       </c>
-      <c r="F10" s="26" t="n">
+      <c r="F10" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A10,分行明細!$F$5:$F$187,"TYPE_3")</f>
         <v>6</v>
       </c>
-      <c r="G10" s="26" t="n">
+      <c r="G10" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A10,分行明細!$F$5:$F$187,"TYPE_4")</f>
         <v>5</v>
       </c>
-      <c r="H10" s="26" t="n">
+      <c r="H10" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A10,分行明細!$F$5:$F$187,"TYPE_5")</f>
         <v>9</v>
       </c>
-      <c r="I10" s="26" t="n">
+      <c r="I10" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A10,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>0</v>
       </c>
-      <c r="J10" s="17" t="n">
+      <c r="J10" s="26" t="n">
         <f aca="false">SUM(D10:I10)</f>
         <v>20</v>
       </c>
-      <c r="K10" s="17" t="n">
+      <c r="K10" s="26" t="n">
         <f aca="false">H10+I10</f>
         <v>9</v>
       </c>
-      <c r="L10" s="17" t="n">
+      <c r="L10" s="26" t="n">
         <f aca="false">I10</f>
         <v>0</v>
       </c>
@@ -18636,48 +19564,48 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>300</v>
-      </c>
-      <c r="D11" s="26" t="n">
+      <c r="B11" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>313</v>
+      </c>
+      <c r="D11" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A11,分行明細!$F$5:$F$187,"TYPE_1")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="26" t="n">
+      <c r="E11" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A11,分行明細!$F$5:$F$187,"TYPE_2")</f>
         <v>1</v>
       </c>
-      <c r="F11" s="26" t="n">
+      <c r="F11" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A11,分行明細!$F$5:$F$187,"TYPE_3")</f>
         <v>9</v>
       </c>
-      <c r="G11" s="26" t="n">
+      <c r="G11" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A11,分行明細!$F$5:$F$187,"TYPE_4")</f>
         <v>10</v>
       </c>
-      <c r="H11" s="26" t="n">
+      <c r="H11" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A11,分行明細!$F$5:$F$187,"TYPE_5")</f>
         <v>13</v>
       </c>
-      <c r="I11" s="26" t="n">
+      <c r="I11" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A11,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>3</v>
       </c>
-      <c r="J11" s="17" t="n">
+      <c r="J11" s="26" t="n">
         <f aca="false">SUM(D11:I11)</f>
         <v>36</v>
       </c>
-      <c r="K11" s="17" t="n">
+      <c r="K11" s="26" t="n">
         <f aca="false">H11+I11</f>
         <v>16</v>
       </c>
-      <c r="L11" s="17" t="n">
+      <c r="L11" s="26" t="n">
         <f aca="false">I11</f>
         <v>3</v>
       </c>
@@ -18687,48 +19615,48 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="27" t="s">
-        <v>301</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>302</v>
-      </c>
-      <c r="D12" s="26" t="n">
+      <c r="B12" s="30" t="s">
+        <v>314</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>315</v>
+      </c>
+      <c r="D12" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A12,分行明細!$F$5:$F$187,"TYPE_1")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="26" t="n">
+      <c r="E12" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A12,分行明細!$F$5:$F$187,"TYPE_2")</f>
         <v>0</v>
       </c>
-      <c r="F12" s="26" t="n">
+      <c r="F12" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A12,分行明細!$F$5:$F$187,"TYPE_3")</f>
         <v>8</v>
       </c>
-      <c r="G12" s="26" t="n">
+      <c r="G12" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A12,分行明細!$F$5:$F$187,"TYPE_4")</f>
         <v>13</v>
       </c>
-      <c r="H12" s="26" t="n">
+      <c r="H12" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A12,分行明細!$F$5:$F$187,"TYPE_5")</f>
         <v>23</v>
       </c>
-      <c r="I12" s="26" t="n">
+      <c r="I12" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A12,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>9</v>
       </c>
-      <c r="J12" s="17" t="n">
+      <c r="J12" s="26" t="n">
         <f aca="false">SUM(D12:I12)</f>
         <v>53</v>
       </c>
-      <c r="K12" s="17" t="n">
+      <c r="K12" s="26" t="n">
         <f aca="false">H12+I12</f>
         <v>32</v>
       </c>
-      <c r="L12" s="17" t="n">
+      <c r="L12" s="26" t="n">
         <f aca="false">I12</f>
         <v>9</v>
       </c>
@@ -18738,48 +19666,48 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="28" t="s">
-        <v>303</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>304</v>
-      </c>
-      <c r="D13" s="26" t="n">
+      <c r="B13" s="31" t="s">
+        <v>316</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>317</v>
+      </c>
+      <c r="D13" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A13,分行明細!$F$5:$F$187,"TYPE_1")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="26" t="n">
+      <c r="E13" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A13,分行明細!$F$5:$F$187,"TYPE_2")</f>
         <v>1</v>
       </c>
-      <c r="F13" s="26" t="n">
+      <c r="F13" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A13,分行明細!$F$5:$F$187,"TYPE_3")</f>
         <v>3</v>
       </c>
-      <c r="G13" s="26" t="n">
+      <c r="G13" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A13,分行明細!$F$5:$F$187,"TYPE_4")</f>
         <v>2</v>
       </c>
-      <c r="H13" s="26" t="n">
+      <c r="H13" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A13,分行明細!$F$5:$F$187,"TYPE_5")</f>
         <v>11</v>
       </c>
-      <c r="I13" s="26" t="n">
+      <c r="I13" s="29" t="n">
         <f aca="false">COUNTIFS(分行明細!$E$5:$E$187,$A13,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>7</v>
       </c>
-      <c r="J13" s="17" t="n">
+      <c r="J13" s="26" t="n">
         <f aca="false">SUM(D13:I13)</f>
         <v>24</v>
       </c>
-      <c r="K13" s="17" t="n">
+      <c r="K13" s="26" t="n">
         <f aca="false">H13+I13</f>
         <v>18</v>
       </c>
-      <c r="L13" s="17" t="n">
+      <c r="L13" s="26" t="n">
         <f aca="false">I13</f>
         <v>7</v>
       </c>
@@ -18789,55 +19717,55 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18" t="n">
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17" t="n">
         <f aca="false">SUM(D5:D13)</f>
         <v>3</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="17" t="n">
         <f aca="false">SUM(E5:E13)</f>
         <v>4</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="17" t="n">
         <f aca="false">SUM(F5:F13)</f>
         <v>40</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="17" t="n">
         <f aca="false">SUM(G5:G13)</f>
         <v>52</v>
       </c>
-      <c r="H14" s="18" t="n">
+      <c r="H14" s="17" t="n">
         <f aca="false">SUM(H5:H13)</f>
         <v>65</v>
       </c>
-      <c r="I14" s="18" t="n">
+      <c r="I14" s="17" t="n">
         <f aca="false">SUM(I5:I13)</f>
         <v>19</v>
       </c>
-      <c r="J14" s="18" t="n">
+      <c r="J14" s="17" t="n">
         <f aca="false">SUM(J5:J13)</f>
         <v>183</v>
       </c>
-      <c r="K14" s="18" t="n">
+      <c r="K14" s="17" t="n">
         <f aca="false">SUM(K5:K13)</f>
         <v>84</v>
       </c>
-      <c r="L14" s="18" t="n">
+      <c r="L14" s="17" t="n">
         <f aca="false">SUM(L5:L13)</f>
         <v>19</v>
       </c>
-      <c r="M14" s="20" t="n">
+      <c r="M14" s="19" t="n">
         <f aca="false">IFERROR(L14/J14,0)</f>
         <v>0.103825136612022</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -18861,7 +19789,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -18878,272 +19806,272 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="29" t="s">
-        <v>312</v>
-      </c>
-      <c r="B4" s="24" t="n">
+      <c r="A4" s="32" t="s">
+        <v>325</v>
+      </c>
+      <c r="B4" s="18" t="n">
         <f aca="false">級距彙總!F16</f>
         <v>11785380000</v>
       </c>
-      <c r="C4" s="30" t="n">
+      <c r="C4" s="33" t="n">
         <f aca="false">B4/100000000</f>
         <v>117.8538</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="17" t="n">
         <f aca="false">級距彙總!D16</f>
         <v>183</v>
       </c>
-      <c r="E4" s="31" t="s">
-        <v>313</v>
+      <c r="E4" s="34" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="31" t="s">
-        <v>314</v>
-      </c>
-      <c r="B5" s="24" t="n">
+      <c r="A5" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="B5" s="18" t="n">
         <f aca="false">級距彙總!K16</f>
         <v>1523166642</v>
       </c>
-      <c r="C5" s="30" t="n">
+      <c r="C5" s="33" t="n">
         <f aca="false">B5/100000000</f>
         <v>15.23166642</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="17" t="n">
         <f aca="false">級距彙總!M16</f>
         <v>99</v>
       </c>
-      <c r="E5" s="31" t="s">
-        <v>315</v>
+      <c r="E5" s="34" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="B6" s="23" t="n">
+      <c r="A6" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="B6" s="15" t="n">
         <f aca="false">級距彙總!K14</f>
         <v>907542432</v>
       </c>
-      <c r="C6" s="32" t="n">
+      <c r="C6" s="35" t="n">
         <f aca="false">B6/100000000</f>
         <v>9.07542432</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="26" t="n">
         <f aca="false">級距彙總!M14</f>
         <v>52</v>
       </c>
-      <c r="E6" s="33" t="s">
-        <v>317</v>
+      <c r="E6" s="21" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
-        <v>318</v>
-      </c>
-      <c r="B7" s="23" t="n">
+      <c r="A7" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="B7" s="15" t="n">
         <f aca="false">級距彙總!K15</f>
         <v>615624210</v>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="35" t="n">
         <f aca="false">B7/100000000</f>
         <v>6.1562421</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="26" t="n">
         <f aca="false">級距彙總!M15</f>
         <v>47</v>
       </c>
-      <c r="E7" s="33" t="s">
-        <v>319</v>
+      <c r="E7" s="21" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="31" t="s">
-        <v>320</v>
-      </c>
-      <c r="B8" s="24" t="n">
+      <c r="A8" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="B8" s="18" t="n">
         <f aca="false">級距彙總!L16</f>
         <v>-822947273</v>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="33" t="n">
         <f aca="false">B8/100000000</f>
         <v>-8.22947273</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="17" t="n">
         <f aca="false">級距彙總!N16</f>
         <v>84</v>
       </c>
-      <c r="E8" s="31" t="s">
-        <v>321</v>
+      <c r="E8" s="34" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="B9" s="23" t="n">
+      <c r="A9" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="B9" s="15" t="n">
         <f aca="false">級距彙總!L14</f>
         <v>-112690144</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="35" t="n">
         <f aca="false">B9/100000000</f>
         <v>-1.12690144</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="26" t="n">
         <f aca="false">級距彙總!N14</f>
         <v>18</v>
       </c>
-      <c r="E9" s="33" t="s">
-        <v>317</v>
+      <c r="E9" s="21" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>318</v>
-      </c>
-      <c r="B10" s="23" t="n">
+      <c r="A10" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="B10" s="15" t="n">
         <f aca="false">級距彙總!L15</f>
         <v>-710257129</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="35" t="n">
         <f aca="false">B10/100000000</f>
         <v>-7.10257129</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="26" t="n">
         <f aca="false">級距彙總!N15</f>
         <v>66</v>
       </c>
-      <c r="E10" s="33" t="s">
-        <v>319</v>
+      <c r="E10" s="21" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
-        <v>322</v>
-      </c>
-      <c r="B11" s="23" t="n">
+      <c r="A11" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="B11" s="15" t="n">
         <f aca="false">級距彙總!L11</f>
         <v>-149319615</v>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="35" t="n">
         <f aca="false">B11/100000000</f>
         <v>-1.49319615</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="26" t="n">
         <f aca="false">級距彙總!N11</f>
         <v>16</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="E11" s="21" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="B12" s="23" t="n">
+      <c r="A12" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="B12" s="15" t="n">
         <f aca="false">級距彙總!L12</f>
         <v>-342631799</v>
       </c>
-      <c r="C12" s="32" t="n">
+      <c r="C12" s="35" t="n">
         <f aca="false">B12/100000000</f>
         <v>-3.42631799</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="26" t="n">
         <f aca="false">級距彙總!N12</f>
         <v>32</v>
       </c>
-      <c r="E12" s="33" t="s">
+      <c r="E12" s="21" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="B13" s="23" t="n">
+      <c r="A13" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="B13" s="15" t="n">
         <f aca="false">級距彙總!L13</f>
         <v>-218305715</v>
       </c>
-      <c r="C13" s="32" t="n">
+      <c r="C13" s="35" t="n">
         <f aca="false">B13/100000000</f>
         <v>-2.18305715</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="26" t="n">
         <f aca="false">級距彙總!N13</f>
         <v>18</v>
       </c>
-      <c r="E13" s="33" t="s">
+      <c r="E13" s="21" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="31" t="s">
-        <v>325</v>
-      </c>
-      <c r="B14" s="24" t="n">
+      <c r="A14" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="B14" s="18" t="n">
         <f aca="false">B4+B5+B8</f>
         <v>12485599369</v>
       </c>
-      <c r="C14" s="30" t="n">
+      <c r="C14" s="33" t="n">
         <f aca="false">B14/100000000</f>
         <v>124.85599369</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="17" t="n">
         <f aca="false">級距彙總!D16</f>
         <v>183</v>
       </c>
-      <c r="E14" s="31" t="s">
-        <v>326</v>
+      <c r="E14" s="34" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="33" t="s">
-        <v>327</v>
+      <c r="A15" s="21" t="s">
+        <v>340</v>
       </c>
       <c r="B15" s="16" t="n">
         <f aca="false">B14/B4</f>
         <v>1.05941423772505</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="21" t="s">
-        <v>328</v>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="23" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
-        <v>329</v>
+      <c r="A16" s="23" t="s">
+        <v>342</v>
       </c>
       <c r="B16" s="16" t="n">
         <f aca="false">B10/B8</f>
         <v>0.863065171126705</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="21" t="s">
-        <v>330</v>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="23" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -19157,7 +20085,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -19174,149 +20102,149 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="B4" s="17" t="n">
+      <c r="A4" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="B4" s="26" t="n">
         <f aca="false">COUNTIFS(分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>19</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="33" t="s">
-        <v>333</v>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="21" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="33" t="s">
-        <v>334</v>
-      </c>
-      <c r="B5" s="23" t="n">
+      <c r="A5" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="B5" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$J$5:$J$187,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>1097730000</v>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="25" t="n">
         <f aca="false">B5/100000000</f>
         <v>10.9773</v>
       </c>
-      <c r="D5" s="34" t="n">
+      <c r="D5" s="36" t="n">
         <f aca="false">B5/B6-1</f>
         <v>0.461482261742834</v>
       </c>
-      <c r="E5" s="33"/>
+      <c r="E5" s="21"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="33" t="s">
-        <v>335</v>
-      </c>
-      <c r="B6" s="23" t="n">
+      <c r="A6" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="B6" s="15" t="n">
         <f aca="false">SUMIFS(分行明細!$K$5:$K$187,分行明細!$F$5:$F$187,"TYPE_6")</f>
         <v>751107303</v>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="25" t="n">
         <f aca="false">B6/100000000</f>
         <v>7.51107303</v>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="D6" s="36" t="n">
         <f aca="false">B6/B6-1</f>
         <v>0</v>
       </c>
-      <c r="E6" s="33"/>
+      <c r="E6" s="21"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="s">
-        <v>327</v>
+      <c r="A7" s="21" t="s">
+        <v>340</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">B6/B5</f>
         <v>0.684236836927113</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="21" t="s">
-        <v>328</v>
+      <c r="C7" s="25"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="23" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="s">
-        <v>336</v>
-      </c>
-      <c r="B8" s="23" t="n">
+      <c r="A8" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="B8" s="15" t="n">
         <f aca="false">B5*B11</f>
         <v>1262389500</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="25" t="n">
         <f aca="false">B8/100000000</f>
         <v>12.623895</v>
       </c>
-      <c r="D8" s="34" t="n">
+      <c r="D8" s="36" t="n">
         <f aca="false">B8/B6-1</f>
         <v>0.680704601004259</v>
       </c>
-      <c r="E8" s="33" t="s">
-        <v>337</v>
+      <c r="E8" s="21" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="s">
-        <v>338</v>
-      </c>
-      <c r="B9" s="23" t="n">
+      <c r="A9" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="B9" s="15" t="n">
         <f aca="false">B6*B12</f>
         <v>773640522.09</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="25" t="n">
         <f aca="false">B9/100000000</f>
         <v>7.7364052209</v>
       </c>
-      <c r="D9" s="34" t="n">
+      <c r="D9" s="36" t="n">
         <f aca="false">B9/B6-1</f>
         <v>0.03</v>
       </c>
-      <c r="E9" s="21" t="s">
-        <v>339</v>
+      <c r="E9" s="23" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="35" t="s">
-        <v>340</v>
-      </c>
-      <c r="B11" s="36" t="n">
+      <c r="A11" s="37" t="s">
+        <v>353</v>
+      </c>
+      <c r="B11" s="38" t="n">
         <v>1.15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="35" t="s">
-        <v>341</v>
-      </c>
-      <c r="B12" s="36" t="n">
+      <c r="A12" s="37" t="s">
+        <v>354</v>
+      </c>
+      <c r="B12" s="38" t="n">
         <v>1.03</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
